--- a/data-EC.xlsx
+++ b/data-EC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\webapps\auto-approve\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1CA9404-6CF3-4DF8-B35B-5FCE2EABF6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52A6860-BF99-4C11-BB63-57B26AA963C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>id_assignment</t>
   </si>
@@ -37,13 +37,304 @@
     <t>keterangan</t>
   </si>
   <si>
-    <t>c710586f-a9a8-45f1-ad61-8174ed68352b</t>
-  </si>
-  <si>
-    <t>b78ce526-676f-40ff-b273-f0917dd3ada9</t>
-  </si>
-  <si>
-    <t>00692bfb-2afb-45ba-ab1f-0a3ba4108234</t>
+    <t>77fd1d55-fb3c-4af6-9f58-8c94a94485ea</t>
+  </si>
+  <si>
+    <t>ea71c009-7ffe-4fcb-a16b-898cfe202eee</t>
+  </si>
+  <si>
+    <t>6c3d6d7a-6574-4047-b19f-cf44d8199b94</t>
+  </si>
+  <si>
+    <t>2a362191-81ac-4f5d-8349-e31899cca7b2</t>
+  </si>
+  <si>
+    <t>887d4cba-ad2b-4504-9517-7102aa20ad18</t>
+  </si>
+  <si>
+    <t>377913f0-8362-40d6-8615-5fd2abb1bd1c</t>
+  </si>
+  <si>
+    <t>f6ecac91-4a66-42a2-9073-87dda31ec960</t>
+  </si>
+  <si>
+    <t>e5e9ce2c-2abd-4d78-97c7-d1b9370c19ba</t>
+  </si>
+  <si>
+    <t>f9a7edea-4353-4f53-a7c6-cf79b2790d76</t>
+  </si>
+  <si>
+    <t>930cf209-80af-4e70-a850-3b65e495a485</t>
+  </si>
+  <si>
+    <t>899e55bb-f2b5-4c09-991a-845d2d7d6965</t>
+  </si>
+  <si>
+    <t>ef8693f0-df20-4a55-99fc-6e06fdc77b2a</t>
+  </si>
+  <si>
+    <t>caa6e18d-08ce-466a-bae5-99951394199a</t>
+  </si>
+  <si>
+    <t>16e7d78b-a170-434d-9185-8bf75cfc27de</t>
+  </si>
+  <si>
+    <t>ac6937bc-c017-4fc7-9de8-97e3783726da</t>
+  </si>
+  <si>
+    <t>7d52930c-6ca9-452e-823a-62b2a28c229f</t>
+  </si>
+  <si>
+    <t>ffcec4bf-e911-408c-b51e-90a719c6055d</t>
+  </si>
+  <si>
+    <t>0351d3ab-b862-46e5-9ebc-f19dd49d178c</t>
+  </si>
+  <si>
+    <t>8413bb72-67c7-43a6-8d6c-1f073fe49ca1</t>
+  </si>
+  <si>
+    <t>32ca1685-c991-4c0b-b68c-2a129aef2466</t>
+  </si>
+  <si>
+    <t>6a22e36d-50a7-446d-b144-d2e7d79942c1</t>
+  </si>
+  <si>
+    <t>0d335a90-1dff-4ddb-9c74-b2b680baaa9b</t>
+  </si>
+  <si>
+    <t>d569b354-c4a3-450c-8547-750aad63a410</t>
+  </si>
+  <si>
+    <t>61662c1a-f27c-4c65-8050-60bd414882e5</t>
+  </si>
+  <si>
+    <t>ff73341f-0a19-4d55-8383-f9042262ccd6</t>
+  </si>
+  <si>
+    <t>47879281-572a-4b19-8372-0465621781ff</t>
+  </si>
+  <si>
+    <t>33b153f0-35e8-443e-ad14-f5fac6248eb6</t>
+  </si>
+  <si>
+    <t>3d27138d-ac92-4e89-8909-99eeb14775f2</t>
+  </si>
+  <si>
+    <t>639cc2ca-ae18-4b08-a483-d236b2f28139</t>
+  </si>
+  <si>
+    <t>d3b603fd-80c6-431c-aa6d-7814e4069517</t>
+  </si>
+  <si>
+    <t>f86e18c4-0da2-4f5c-92f4-da32af99cc27</t>
+  </si>
+  <si>
+    <t>d49bd49a-1b08-43e0-97d5-5803d17e156e</t>
+  </si>
+  <si>
+    <t>089b38dc-4526-4990-a29b-5286faacd71e</t>
+  </si>
+  <si>
+    <t>f28ff454-8b06-409b-893a-82f637c5a3b9</t>
+  </si>
+  <si>
+    <t>52093a80-2508-43e4-b544-c21e4f2900f0</t>
+  </si>
+  <si>
+    <t>e875a13d-edca-45a0-bfcb-24f9e5739a25</t>
+  </si>
+  <si>
+    <t>a4e15053-796f-4402-9665-33364564d5b7</t>
+  </si>
+  <si>
+    <t>b340849b-1234-435c-8d4e-02d9d585beab</t>
+  </si>
+  <si>
+    <t>741a4e16-37eb-4251-830c-966c0f0871a5</t>
+  </si>
+  <si>
+    <t>f0eb437f-c2ca-42fe-8ab1-7bc22d466c17</t>
+  </si>
+  <si>
+    <t>d0ee4219-9cb2-41de-98f4-2e90b60e9767</t>
+  </si>
+  <si>
+    <t>4d1c0749-c196-447c-b3b4-2605fb2f3a54</t>
+  </si>
+  <si>
+    <t>add09e6e-9e53-482d-80c6-e7230bed0d3d</t>
+  </si>
+  <si>
+    <t>e2f61456-9f66-49ef-88c7-93c53963fb8c</t>
+  </si>
+  <si>
+    <t>6b4076ef-77d5-40fd-b50b-c03ae88867d7</t>
+  </si>
+  <si>
+    <t>3ba71c0c-2f5e-4946-9f23-a9b06a375d2b</t>
+  </si>
+  <si>
+    <t>fc2bfa58-71dd-486c-8f3c-2ce7ae76100d</t>
+  </si>
+  <si>
+    <t>f406e980-57f7-4040-874b-7068c2e9e70c</t>
+  </si>
+  <si>
+    <t>98eda532-0491-4941-99f3-2152b5d1d418</t>
+  </si>
+  <si>
+    <t>99b6fa22-8185-46c2-8be4-1b37aed67f66</t>
+  </si>
+  <si>
+    <t>847d5f4a-5c94-4f34-b2bc-4d058f5a6d4e</t>
+  </si>
+  <si>
+    <t>5684e738-e9d8-470f-9b18-8f8e03e12d65</t>
+  </si>
+  <si>
+    <t>a7454d8d-fba3-4a2e-bc03-b54e227ad889</t>
+  </si>
+  <si>
+    <t>28172fc9-8a6e-4059-9d2c-2c5b2ed1e57b</t>
+  </si>
+  <si>
+    <t>7f561542-1069-4bdb-8998-888ed9a12e42</t>
+  </si>
+  <si>
+    <t>2c10e2fd-b2d9-47bd-b856-91ec477a4086</t>
+  </si>
+  <si>
+    <t>fef5aa9c-2893-4c12-97c4-9980e3cf0d41</t>
+  </si>
+  <si>
+    <t>b048a3b6-81d4-4152-bf80-2a539121c249</t>
+  </si>
+  <si>
+    <t>4b4c34c1-a07e-401a-b2b1-71f72ffe2bf1</t>
+  </si>
+  <si>
+    <t>88b11dba-64c7-43fd-bfd9-01c1e8c3aabf</t>
+  </si>
+  <si>
+    <t>8a556c1f-7510-4faf-9b22-90ed950e09fb</t>
+  </si>
+  <si>
+    <t>76ec9ee5-96ca-4518-9d50-bca6a37efa3e</t>
+  </si>
+  <si>
+    <t>aa7369fa-2858-43d9-a019-b6421fdf2f55</t>
+  </si>
+  <si>
+    <t>dea5af80-e1f8-47da-924e-1e6d9ccd789f</t>
+  </si>
+  <si>
+    <t>2f3b73df-8f83-459d-bb35-c71929ba977e</t>
+  </si>
+  <si>
+    <t>db8b8462-f8e9-4926-9717-816fddd4392c</t>
+  </si>
+  <si>
+    <t>eb161aae-8bf6-498f-95fc-23be2a7f04bb</t>
+  </si>
+  <si>
+    <t>15664849-92f1-4791-9d3e-d156a8940b9b</t>
+  </si>
+  <si>
+    <t>15c3a166-1dfe-40e3-82b9-216762f5bf5a</t>
+  </si>
+  <si>
+    <t>bd14aa6f-c6e4-44a1-bcaf-362bdeb5767d</t>
+  </si>
+  <si>
+    <t>104fdc57-8f4d-4ff4-afcc-74dbc4508df2</t>
+  </si>
+  <si>
+    <t>cf63ec92-fbb6-48b7-9b64-83217c8aa039</t>
+  </si>
+  <si>
+    <t>1228d9bf-0b42-4a66-97e8-0cc6a70a0f52</t>
+  </si>
+  <si>
+    <t>dcbedc52-c9a8-4a78-abfd-1a3c7d9886f9</t>
+  </si>
+  <si>
+    <t>8530a545-da20-4441-be1b-17253e7e3c4b</t>
+  </si>
+  <si>
+    <t>c2156ba0-a772-4fc1-87ac-6a56f6643a28</t>
+  </si>
+  <si>
+    <t>122a6f26-e6e0-41ae-940d-d2afe429c930</t>
+  </si>
+  <si>
+    <t>591a7902-71e1-48dc-9fec-1ffab784ae9f</t>
+  </si>
+  <si>
+    <t>bfbd1e0d-34f8-480c-a7f5-76305b9579d3</t>
+  </si>
+  <si>
+    <t>5b8e69a1-1d39-427f-8d23-57f4429cd0b3</t>
+  </si>
+  <si>
+    <t>38530156-39be-4c3f-a21f-122c06b811e3</t>
+  </si>
+  <si>
+    <t>abb0e497-52ad-4d82-83cf-eb78533d7459</t>
+  </si>
+  <si>
+    <t>9ed1a461-4dcb-4dfa-9b5c-3c1bc4d5d0d6</t>
+  </si>
+  <si>
+    <t>2485fb59-e639-4b65-82bd-c2c502347183</t>
+  </si>
+  <si>
+    <t>7c57c172-6ccf-42b8-bcc1-a2f02970703f</t>
+  </si>
+  <si>
+    <t>902701cc-c144-4a39-a7a0-e9e23a79e577</t>
+  </si>
+  <si>
+    <t>b4a01c91-1bfd-4488-aac0-b37fe30aaaa3</t>
+  </si>
+  <si>
+    <t>297dd004-3c17-4971-8348-86e1c547c140</t>
+  </si>
+  <si>
+    <t>6bf5974f-0472-4939-b932-2a6fb71cac2d</t>
+  </si>
+  <si>
+    <t>996dc9a0-af46-444b-9d4b-5793773a11f3</t>
+  </si>
+  <si>
+    <t>acc85655-3c8c-48e2-b1c4-1eb6eb16bd8d</t>
+  </si>
+  <si>
+    <t>7a69fb2a-23dc-4b94-82ce-6e0afdd8ab6f</t>
+  </si>
+  <si>
+    <t>bc64b3c1-c899-4f2c-82b2-dc80bda9a4aa</t>
+  </si>
+  <si>
+    <t>efd20c8e-65f0-4c3c-9031-90f56cf8cbfc</t>
+  </si>
+  <si>
+    <t>985da4e1-e21a-4a5d-8ba1-cf666a137b99</t>
+  </si>
+  <si>
+    <t>469436e3-60d2-45c2-ae3b-16c2ce97eb0f</t>
+  </si>
+  <si>
+    <t>f95747da-3297-483a-8076-9d862ee50153</t>
+  </si>
+  <si>
+    <t>e3c070fe-b24c-4165-89ed-0e040b892551</t>
+  </si>
+  <si>
+    <t>85468224-f15b-41f0-a82a-a4412a620408</t>
+  </si>
+  <si>
+    <t>c17389bf-33dc-4204-a0d7-d4c6a7a4791d</t>
   </si>
 </sst>
 </file>
@@ -79,8 +370,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -415,7 +707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
@@ -454,7 +746,493 @@
         <v>7</v>
       </c>
     </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data-EC.xlsx
+++ b/data-EC.xlsx
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>SUCCESS</t>
         </is>
       </c>
     </row>
@@ -2464,6 +2464,11 @@
           <t>f5bc30ed-80b4-46ef-bf23-156206b50034</t>
         </is>
       </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2471,6 +2476,11 @@
           <t>04b0adcb-d5bd-4ff2-8b6b-de64e87c9aa0</t>
         </is>
       </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2478,6 +2488,11 @@
           <t>b67d0f5e-3026-46c4-899b-cfa92e4c842f</t>
         </is>
       </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2485,6 +2500,11 @@
           <t>7b2fdbe3-c221-4fc3-8056-9161142247f0</t>
         </is>
       </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2492,6 +2512,11 @@
           <t>4e4d50c1-ac72-4aff-b903-4add880f6585</t>
         </is>
       </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -2499,6 +2524,11 @@
           <t>ee7e87f7-8208-4304-b2fb-63d4ae7b6fb8</t>
         </is>
       </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2506,6 +2536,11 @@
           <t>b523bdbe-54b8-49e5-b39e-30c2a04ece6b</t>
         </is>
       </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2513,6 +2548,11 @@
           <t>8aecd013-0595-484f-a4a1-be8ae8e90728</t>
         </is>
       </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2520,6 +2560,11 @@
           <t>8102867d-1bc6-47e2-af80-98606cd74e9e</t>
         </is>
       </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2527,6 +2572,11 @@
           <t>85912c2a-081c-4d54-a3c3-e8cf9b2ae538</t>
         </is>
       </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2534,6 +2584,11 @@
           <t>150555f2-f46f-4dab-845c-89806fd53b15</t>
         </is>
       </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2541,6 +2596,11 @@
           <t>a38ff132-9a06-486d-9a3b-b12a8b8f22d5</t>
         </is>
       </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2548,6 +2608,11 @@
           <t>d4ed17f2-5ba8-4f78-8db2-0bd7aaabe8c2</t>
         </is>
       </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2555,6 +2620,11 @@
           <t>fcdcc989-5632-4962-a2e8-b562adb1f2be</t>
         </is>
       </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -2562,6 +2632,11 @@
           <t>1d33016d-a86e-459c-b86d-0f85d8051dc0</t>
         </is>
       </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2569,6 +2644,16 @@
           <t>efa069eb-00a3-41ad-92ba-08e797b4a50c</t>
         </is>
       </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>NO_CHANGE</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Ringkasan sudah dimuat tanpa tombol Approve</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2576,6 +2661,16 @@
           <t>53b1f7e5-01df-4ad7-bd5f-abd711cccb42</t>
         </is>
       </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>NO_CHANGE</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Ringkasan sudah dimuat tanpa tombol Approve</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2583,6 +2678,16 @@
           <t>f0f9228e-77bb-47b3-a873-db44725c4f06</t>
         </is>
       </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>NO_CHANGE</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Ringkasan sudah dimuat tanpa tombol Approve</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2590,6 +2695,16 @@
           <t>5e82b1c0-a00b-4bee-93ba-4ee68dbcbbef</t>
         </is>
       </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>NO_CHANGE</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Ringkasan sudah dimuat tanpa tombol Approve</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2597,6 +2712,16 @@
           <t>584295ca-8c81-4071-ab56-80e4784dd0be</t>
         </is>
       </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>NO_CHANGE</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Ringkasan sudah dimuat tanpa tombol Approve</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2604,6 +2729,16 @@
           <t>81b42a93-20d4-426c-8097-8cd41b7ed0d8</t>
         </is>
       </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>NO_CHANGE</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Ringkasan sudah dimuat tanpa tombol Approve</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -2611,6 +2746,16 @@
           <t>8fd36dfe-67fd-4559-acd4-efb94927997d</t>
         </is>
       </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>NO_CHANGE</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Ringkasan sudah dimuat tanpa tombol Approve</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -2618,6 +2763,11 @@
           <t>c0b88261-3978-4b2d-a08e-c5d8ee3f4029</t>
         </is>
       </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -2625,6 +2775,11 @@
           <t>b2a0b561-4a29-43ae-81d9-3a8856a3c9af</t>
         </is>
       </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -2632,6 +2787,11 @@
           <t>bfcd79d0-45c9-481a-8905-f060fb481485</t>
         </is>
       </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -2639,6 +2799,11 @@
           <t>87213853-d223-4ddb-a75e-ec2caf1d75f9</t>
         </is>
       </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2646,6 +2811,11 @@
           <t>11a60d58-eeef-4c8d-8a0e-dc1191087df0</t>
         </is>
       </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -2653,6 +2823,11 @@
           <t>3aa79e40-1fe4-4d2b-9fb3-c9e97e04402f</t>
         </is>
       </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -2660,6 +2835,11 @@
           <t>88fd225a-4934-4f23-8d68-962f43db4ae4</t>
         </is>
       </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -2667,6 +2847,11 @@
           <t>ea453387-7a34-41ec-93b2-a3979a68c8b2</t>
         </is>
       </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -2674,6 +2859,11 @@
           <t>10e1a5f9-2fa3-41bd-8655-6469177c4c00</t>
         </is>
       </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -2681,6 +2871,11 @@
           <t>e8fadcc1-5b1c-4000-9a31-fca33d513a8f</t>
         </is>
       </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -2688,6 +2883,11 @@
           <t>fc1de1ff-d72c-4564-878e-ab503e893af2</t>
         </is>
       </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -2695,6 +2895,11 @@
           <t>ab117b38-8122-4422-a227-ccc21dd58688</t>
         </is>
       </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -2702,6 +2907,11 @@
           <t>90127b50-eed4-40fa-ae37-3180733ebe44</t>
         </is>
       </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -2709,6 +2919,11 @@
           <t>f45a67c0-474a-45ff-bc4f-93588c2b2ebc</t>
         </is>
       </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -2716,6 +2931,11 @@
           <t>d205a4a9-5641-4b1e-b8d2-9f38055059d4</t>
         </is>
       </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -2723,6 +2943,11 @@
           <t>4f7daf4a-4280-4845-8699-4e1db8ab3be1</t>
         </is>
       </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -2730,6 +2955,11 @@
           <t>e77b9c99-fd75-4a10-b4e1-89ced05c787c</t>
         </is>
       </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -2737,6 +2967,11 @@
           <t>c413af9a-b537-48fb-a8b4-7b6fac3c8119</t>
         </is>
       </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -2744,6 +2979,11 @@
           <t>11bcd9bd-3a37-45e0-83e1-8bc64d0cde2a</t>
         </is>
       </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -2751,6 +2991,11 @@
           <t>8fa3ac84-b02d-4cf0-a621-62e5d242cbed</t>
         </is>
       </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -2758,6 +3003,11 @@
           <t>852395ae-6414-4afc-bfc9-45e0e7410c86</t>
         </is>
       </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -2765,6 +3015,11 @@
           <t>c217f655-8367-470d-88be-5aeabbc06c1a</t>
         </is>
       </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -2772,6 +3027,11 @@
           <t>6ab413ec-6a82-48f0-9fff-c0598df5175e</t>
         </is>
       </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -2779,6 +3039,11 @@
           <t>da38ad92-6086-40c0-afc5-7d31263386a3</t>
         </is>
       </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -2786,6 +3051,11 @@
           <t>e0ebe9ca-b346-438a-89d5-2da2a4272638</t>
         </is>
       </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -2793,6 +3063,11 @@
           <t>860a19a7-ea65-46b3-b93d-b00f46dc1a8a</t>
         </is>
       </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -2800,6 +3075,11 @@
           <t>af284029-0232-4817-9daa-e3311fe502e9</t>
         </is>
       </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -2807,6 +3087,11 @@
           <t>b2ff89bd-9ab0-4455-9343-7a604f130012</t>
         </is>
       </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -2814,6 +3099,11 @@
           <t>d6d0e247-a7c7-4461-a735-74ffcae3b9bc</t>
         </is>
       </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -2821,6 +3111,11 @@
           <t>23e1e8e3-673e-4061-bca6-590c18e63e15</t>
         </is>
       </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -2828,6 +3123,11 @@
           <t>5341251e-95c5-461d-a1df-3d70c2bb8dba</t>
         </is>
       </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -2835,6 +3135,11 @@
           <t>c8092b3b-6ec8-4f69-831f-9e8a3aa53f34</t>
         </is>
       </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -2842,6 +3147,11 @@
           <t>1f2d0a03-8fad-4cc9-bf64-18adeddbb9d9</t>
         </is>
       </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -2849,6 +3159,11 @@
           <t>7faee8f3-5546-4d37-8709-55ea2aceb674</t>
         </is>
       </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -2856,6 +3171,11 @@
           <t>c4a713af-f7c5-492b-9550-de878d484c98</t>
         </is>
       </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -2863,6 +3183,11 @@
           <t>6c9fa5c2-992d-4503-a404-e835396470b9</t>
         </is>
       </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -2870,6 +3195,11 @@
           <t>2947bef2-f7cf-4a38-9455-14a4ea219a52</t>
         </is>
       </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -2877,6 +3207,11 @@
           <t>73799eb0-7edf-429a-85fe-50e9ee626344</t>
         </is>
       </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -2884,6 +3219,11 @@
           <t>224f6878-a2f9-45d7-b663-d23506f0811a</t>
         </is>
       </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -2891,6 +3231,11 @@
           <t>354668e0-2078-41b9-9ecf-8ec34a3c3f74</t>
         </is>
       </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -2898,6 +3243,11 @@
           <t>645f80d3-225c-4c27-b44b-626f870fd242</t>
         </is>
       </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -2905,6 +3255,11 @@
           <t>900e0a82-01e8-48d5-8ca2-5a6694e838e8</t>
         </is>
       </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -2912,6 +3267,11 @@
           <t>66dc95af-f334-4a66-8725-522985271521</t>
         </is>
       </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -2919,6 +3279,11 @@
           <t>9735a7b6-a449-4a52-b596-7e20bd786427</t>
         </is>
       </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -2926,6 +3291,11 @@
           <t>9df94f7d-64c2-4b6f-b1d7-64cb24bf7c8d</t>
         </is>
       </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -2933,6 +3303,11 @@
           <t>9531b718-abf7-4e10-a1ae-5450293c67b8</t>
         </is>
       </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -2940,6 +3315,11 @@
           <t>5044d807-82a8-4866-9317-6b693c5b666c</t>
         </is>
       </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -2947,6 +3327,11 @@
           <t>4c7dd571-1077-4fe5-b099-cccbe4600312</t>
         </is>
       </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -2954,6 +3339,11 @@
           <t>d258a0d4-a379-4163-8dcc-cad912961c5e</t>
         </is>
       </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -2961,6 +3351,11 @@
           <t>2f631131-2be6-429e-b22e-08ebc4fc6e4a</t>
         </is>
       </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
@@ -2968,6 +3363,11 @@
           <t>6e861e5e-bf11-4af7-a6d4-59dba944bead</t>
         </is>
       </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -2975,6 +3375,11 @@
           <t>6d19ef01-dd8e-4bd9-89f1-ab51d7e77dcf</t>
         </is>
       </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -2982,6 +3387,11 @@
           <t>0776d259-1170-45e9-a635-0d9ffd4e498e</t>
         </is>
       </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -2989,6 +3399,11 @@
           <t>d43eef58-19e3-4b50-9910-b61ce4e041ca</t>
         </is>
       </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -2996,6 +3411,11 @@
           <t>7f6b9eaa-b902-487d-87c3-8514394a6e7b</t>
         </is>
       </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
@@ -3003,6 +3423,11 @@
           <t>571e4485-d02b-40c7-8d2a-a87aa9f792db</t>
         </is>
       </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -3010,6 +3435,11 @@
           <t>19da7532-81d4-4908-bf01-8cc4bf1de47a</t>
         </is>
       </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -3017,6 +3447,11 @@
           <t>c2a7c46e-e16c-4419-a3ce-9c55b567c0d4</t>
         </is>
       </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -3024,6 +3459,11 @@
           <t>7186530e-dd63-4a8a-a8a4-73fe8e5aab09</t>
         </is>
       </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -3031,6 +3471,11 @@
           <t>1a9e46ab-b226-47f0-9aa1-5777c789e769</t>
         </is>
       </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -3038,6 +3483,11 @@
           <t>ff9b422e-37d2-47a9-9a97-d2ba533896e4</t>
         </is>
       </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -3045,6 +3495,11 @@
           <t>d5b4fa99-f7f6-4c7f-8505-f01bb30eaab4</t>
         </is>
       </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -3052,6 +3507,11 @@
           <t>5a81ee72-01b2-447f-87a4-51bd0bfa7d8c</t>
         </is>
       </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -3059,6 +3519,11 @@
           <t>6accbf89-89f1-425e-abd9-4712e686cdd4</t>
         </is>
       </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -3066,6 +3531,11 @@
           <t>fd8e3d2d-d1e2-41f2-ba95-13348fb0979f</t>
         </is>
       </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -3073,6 +3543,11 @@
           <t>274de35f-27ef-4f4c-b2c7-e6657d3c0dff</t>
         </is>
       </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -3080,6 +3555,11 @@
           <t>fdc775e1-9594-45b3-b2b6-282fe7e4a9ff</t>
         </is>
       </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -3087,6 +3567,11 @@
           <t>330e5f36-70bb-4f2a-8bbf-bd7d6e6a7c5c</t>
         </is>
       </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -3094,6 +3579,11 @@
           <t>7a4a5272-81b7-4b5e-b001-226f58efdefb</t>
         </is>
       </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -3101,6 +3591,11 @@
           <t>5c8f948d-6e46-46b8-b105-c65c23833b04</t>
         </is>
       </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -3108,6 +3603,11 @@
           <t>72618777-0eb5-443f-836b-41f6ea5d4038</t>
         </is>
       </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -3115,6 +3615,11 @@
           <t>e7557e1b-aa37-4247-8c49-00e8ee90f2a2</t>
         </is>
       </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -3122,6 +3627,11 @@
           <t>da5c1f59-1b96-4ecd-a3fe-7a5646a852ea</t>
         </is>
       </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -3129,6 +3639,11 @@
           <t>d0837ce5-52b6-4366-9722-62f2a8a4acfd</t>
         </is>
       </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -3136,6 +3651,11 @@
           <t>7e3d41f0-5665-405b-8e49-4ffa4e208116</t>
         </is>
       </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -3143,6 +3663,11 @@
           <t>2d342198-86ba-4296-bce3-9598386433df</t>
         </is>
       </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -3150,6 +3675,11 @@
           <t>d15e82f5-15f9-4258-9372-8b5deeb47474</t>
         </is>
       </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -3157,6 +3687,11 @@
           <t>d7655b02-2e1f-459b-947f-483e221fb510</t>
         </is>
       </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -3164,6 +3699,11 @@
           <t>92143418-2517-4dd5-9379-29827ce3946e</t>
         </is>
       </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -3171,6 +3711,11 @@
           <t>bf6de498-1653-4330-a880-729abfdb9fd4</t>
         </is>
       </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -3178,6 +3723,11 @@
           <t>4a52d895-7913-4ff8-a007-b727bcb7d647</t>
         </is>
       </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -3185,6 +3735,11 @@
           <t>db327854-444b-4ada-ae37-c9bcd1e227e6</t>
         </is>
       </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -3192,6 +3747,11 @@
           <t>313fbe50-70c1-4087-92b7-a279f4157ae9</t>
         </is>
       </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -3199,6 +3759,11 @@
           <t>ba46173c-b2d8-4e5e-b7bf-fb1dca8a1cd4</t>
         </is>
       </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -3206,6 +3771,11 @@
           <t>47ec82c7-7a2b-423a-8586-256dca84ec60</t>
         </is>
       </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -3213,6 +3783,11 @@
           <t>0d5ee835-bdfa-4f17-b0c7-f541a5a78a46</t>
         </is>
       </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -3220,6 +3795,11 @@
           <t>1fec4bea-4405-404c-9179-41c0ea733ac7</t>
         </is>
       </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -3227,6 +3807,11 @@
           <t>e05c8c33-9184-449d-b712-9f3489aabb93</t>
         </is>
       </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -3234,6 +3819,11 @@
           <t>fc884f82-6fa9-40e7-9fa9-11c20812bd8b</t>
         </is>
       </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -3241,6 +3831,11 @@
           <t>603ef536-51c9-4716-a102-2da6edc2dcd6</t>
         </is>
       </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -3248,6 +3843,11 @@
           <t>6a828d4e-9a9a-4e72-bc77-118384b0284b</t>
         </is>
       </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -3255,6 +3855,11 @@
           <t>d9cafe56-dc48-49f9-9d83-7b37333b18e3</t>
         </is>
       </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -3262,6 +3867,11 @@
           <t>ee9b2efd-c5f9-4d93-989c-3edda0c3ff77</t>
         </is>
       </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -3269,6 +3879,11 @@
           <t>0eccf629-4093-4ba5-a99d-3b197dc40106</t>
         </is>
       </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -3276,6 +3891,11 @@
           <t>1c57ff67-08a4-4d9e-a1c1-8a6a945c4a63</t>
         </is>
       </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -3283,6 +3903,11 @@
           <t>4c484217-cba1-43b6-af3e-f364935b83f1</t>
         </is>
       </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -3290,6 +3915,11 @@
           <t>15d7f65f-c376-4690-8c96-be05848538f0</t>
         </is>
       </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -3297,6 +3927,11 @@
           <t>16fdd465-569c-4902-92f3-a584131a5859</t>
         </is>
       </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -3304,6 +3939,11 @@
           <t>35672cfb-2c0c-4e21-a00c-159d7b50c32a</t>
         </is>
       </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -3311,6 +3951,11 @@
           <t>609364fd-7d49-43c8-99ea-3486084df81b</t>
         </is>
       </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -3318,6 +3963,11 @@
           <t>82ac92b6-d492-4120-bbc3-8324bda4ab82</t>
         </is>
       </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -3325,6 +3975,11 @@
           <t>78dc6591-7976-4690-b59f-fe3cd5a4c1db</t>
         </is>
       </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -3332,6 +3987,11 @@
           <t>cbde5b9c-8149-4980-a5fa-ce398aee15d6</t>
         </is>
       </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -3339,6 +3999,11 @@
           <t>0baf478e-b2e9-4567-9611-ce635a2c34bd</t>
         </is>
       </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -3346,6 +4011,11 @@
           <t>5993b698-c930-4fe6-bc70-a04e6513b530</t>
         </is>
       </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -3353,6 +4023,11 @@
           <t>e68c6c37-7f92-4716-870f-84c04688ed8c</t>
         </is>
       </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -3360,6 +4035,11 @@
           <t>5705ba26-4f56-43e7-bf50-3c276e85675b</t>
         </is>
       </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -3367,6 +4047,11 @@
           <t>7e065b2d-e86a-40d7-a528-639e0fa14e1c</t>
         </is>
       </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -3374,6 +4059,16 @@
           <t>7e065b2d-e86a-40d7-a528-639e0fa14e1c</t>
         </is>
       </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>NO_CHANGE</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Ringkasan sudah dimuat tanpa tombol Approve</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -3381,6 +4076,11 @@
           <t>bd6d319b-f79a-468f-9d38-6b2d19d312b5</t>
         </is>
       </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -3388,6 +4088,11 @@
           <t>e2c00e83-29b2-4a42-b731-a37adeda7e97</t>
         </is>
       </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -3395,6 +4100,11 @@
           <t>ba5dfbbc-9423-40ae-89bf-7f3f12205be7</t>
         </is>
       </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -3402,6 +4112,11 @@
           <t>0a471681-6292-41b0-af03-65651469b567</t>
         </is>
       </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -3409,6 +4124,11 @@
           <t>21db5a69-d98b-43b9-b28b-b4c21a433cdf</t>
         </is>
       </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -3416,6 +4136,11 @@
           <t>a10cc23a-5dc6-4d85-8ba9-9439e634feda</t>
         </is>
       </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -3423,6 +4148,11 @@
           <t>8b501f56-232e-4c89-ba5e-332a9359f851</t>
         </is>
       </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -3430,6 +4160,16 @@
           <t>efbea355-60a9-4357-a228-3bc8c8c318dd</t>
         </is>
       </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>NO_CHANGE</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Ringkasan sudah dimuat tanpa tombol Approve</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -3437,6 +4177,16 @@
           <t>7244e8c9-6b3b-4f43-8d21-7180af6508ec</t>
         </is>
       </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>NO_CHANGE</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Ringkasan sudah dimuat tanpa tombol Approve</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -3444,6 +4194,11 @@
           <t>6dd58bc9-6616-4333-9958-dbe23185f7b4</t>
         </is>
       </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -3451,6 +4206,11 @@
           <t>65884297-995c-4eac-94f4-cbd996c2ea95</t>
         </is>
       </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -3458,6 +4218,16 @@
           <t>9da01cd3-1d07-40c8-b442-fb4f4594bc2d</t>
         </is>
       </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>NO_CHANGE</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Ringkasan sudah dimuat tanpa tombol Approve</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -3465,6 +4235,16 @@
           <t>3e9e1214-b2c4-4fd9-b0dd-8c7015edd210</t>
         </is>
       </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>NO_CHANGE</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Ringkasan sudah dimuat tanpa tombol Approve</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -3472,6 +4252,11 @@
           <t>ea9c93fa-21b8-42c8-8bcc-df876fcbd607</t>
         </is>
       </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -3479,6 +4264,11 @@
           <t>b349f538-a403-4789-abc0-6f8eae5b640c</t>
         </is>
       </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -3486,6 +4276,11 @@
           <t>c96bbaf4-9697-4f32-8c0a-5973632adb08</t>
         </is>
       </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -3493,11 +4288,21 @@
           <t>7473344f-04a7-4222-9e09-c11a9816590d</t>
         </is>
       </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
           <t>f9a91c1a-6604-4365-a3bd-e0877324f698</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
         </is>
       </c>
     </row>
